--- a/data/hrm_sync_actual_5.xlsx
+++ b/data/hrm_sync_actual_5.xlsx
@@ -103,27 +103,27 @@
     <t>Đã duyệt</t>
   </si>
   <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>19/09/2026 22:00:00</t>
   </si>
   <si>
     <t>20/09/2026 06:00:00</t>
   </si>
   <si>
-    <t>02224358</t>
-  </si>
-  <si>
-    <t>Hoàng Trung Hiếu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
     <t>ca1 tăng ca sản xuất</t>
   </si>
   <si>
@@ -145,16 +145,16 @@
     <t>26/09/2026 06:00:00</t>
   </si>
   <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:00:00</t>
+  </si>
+  <si>
     <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
   </si>
 </sst>
 </file>
@@ -689,10 +689,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
@@ -701,7 +701,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -710,19 +710,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J4" s="8">
         <v>480</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -737,10 +737,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>19</v>
@@ -749,7 +749,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>19</v>
@@ -893,7 +893,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
@@ -902,19 +902,19 @@
         <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J8" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
@@ -950,16 +950,16 @@
         <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>45</v>
       </c>
       <c r="J9" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>45</v>

--- a/data/hrm_sync_actual_5.xlsx
+++ b/data/hrm_sync_actual_5.xlsx
@@ -12,7 +12,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet!$A$2:$I$6333</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet!$2:$2</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -68,93 +68,6 @@
   </si>
   <si>
     <t>Trạng thái duyệt</t>
-  </si>
-  <si>
-    <t>02228947</t>
-  </si>
-  <si>
-    <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>26/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>26/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02224358</t>
-  </si>
-  <si>
-    <t>Hoàng Trung Hiếu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>ca1 tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02226596</t>
-  </si>
-  <si>
-    <t>Đoàn Văn Dương</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>26/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
   </si>
 </sst>
 </file>
@@ -640,340 +553,130 @@
       </c>
     </row>
     <row r="3" s="2" customFormat="1">
-      <c r="A3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="8">
-        <v>480</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
       <c r="N3" s="7"/>
-      <c r="O3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="8">
-        <v>480</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="8">
-        <v>0</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="7"/>
-      <c r="O4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="8">
-        <v>480</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="7"/>
-      <c r="O5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="8">
-        <v>480</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="8">
-        <v>0</v>
-      </c>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="7"/>
-      <c r="O6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="8">
-        <v>480</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="7"/>
-      <c r="O7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="8">
-        <v>120</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8" s="8">
-        <v>0</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="7"/>
-      <c r="O8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="8">
-        <v>480</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="7"/>
-      <c r="O9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7"/>

--- a/data/hrm_sync_actual_5.xlsx
+++ b/data/hrm_sync_actual_5.xlsx
@@ -12,7 +12,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet!$A$2:$I$6333</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -68,6 +68,93 @@
   </si>
   <si>
     <t>Trạng thái duyệt</t>
+  </si>
+  <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>26/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>ca1 tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>26/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:00:00</t>
   </si>
 </sst>
 </file>
@@ -553,130 +640,340 @@
       </c>
     </row>
     <row r="3" s="2" customFormat="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="A3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="8">
+        <v>480</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
       <c r="N3" s="7"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
+      <c r="O3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="8">
+        <v>480</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
       <c r="N4" s="7"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
+      <c r="O4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
+      <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="8">
+        <v>480</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
       <c r="N5" s="7"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
+      <c r="O5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="8">
+        <v>480</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="8">
+        <v>480</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="8">
+        <v>480</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="8">
+        <v>120</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7"/>

--- a/data/hrm_sync_actual_5.xlsx
+++ b/data/hrm_sync_actual_5.xlsx
@@ -12,7 +12,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet!$A$2:$I$6333</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet!$2:$2</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -68,93 +68,6 @@
   </si>
   <si>
     <t>Trạng thái duyệt</t>
-  </si>
-  <si>
-    <t>02228947</t>
-  </si>
-  <si>
-    <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>26/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>26/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02224358</t>
-  </si>
-  <si>
-    <t>Hoàng Trung Hiếu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>ca1 tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>02226596</t>
-  </si>
-  <si>
-    <t>Đoàn Văn Dương</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>26/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
   </si>
 </sst>
 </file>
@@ -640,340 +553,130 @@
       </c>
     </row>
     <row r="3" s="2" customFormat="1">
-      <c r="A3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="8">
-        <v>480</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
       <c r="N3" s="7"/>
-      <c r="O3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="8">
-        <v>480</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="8">
-        <v>0</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="7"/>
-      <c r="O4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="8">
-        <v>480</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="7"/>
-      <c r="O5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="8">
-        <v>480</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="8">
-        <v>0</v>
-      </c>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="7"/>
-      <c r="O6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="8">
-        <v>480</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="7"/>
-      <c r="O7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="8">
-        <v>480</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" s="8">
-        <v>0</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="7"/>
-      <c r="O8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="8">
-        <v>120</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="7"/>
-      <c r="O9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7"/>

--- a/data/hrm_sync_actual_5.xlsx
+++ b/data/hrm_sync_actual_5.xlsx
@@ -12,7 +12,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet!$A$2:$I$6333</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -68,6 +68,39 @@
   </si>
   <si>
     <t>Trạng thái duyệt</t>
+  </si>
+  <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>10/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
   </si>
 </sst>
 </file>
@@ -553,22 +586,52 @@
       </c>
     </row>
     <row r="3" s="2" customFormat="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="A3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="8">
+        <v>480</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
       <c r="N3" s="7"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
+      <c r="O3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7"/>

--- a/data/hrm_sync_actual_5.xlsx
+++ b/data/hrm_sync_actual_5.xlsx
@@ -101,6 +101,36 @@
   </si>
   <si>
     <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca3 tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>17/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>17/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 14:00:00</t>
   </si>
 </sst>
 </file>
@@ -634,58 +664,148 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="8">
+        <v>480</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
       <c r="N4" s="7"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
+      <c r="O4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
+      <c r="A5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="8">
+        <v>480</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
       <c r="N5" s="7"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
+      <c r="O5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="8">
+        <v>480</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7"/>
